--- a/temp_doc/PESERTA UJIAN FIX ADMIN - XI DKV.xlsx
+++ b/temp_doc/PESERTA UJIAN FIX ADMIN - XI DKV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096F2E15-C0E1-C54E-9A0E-982EA7569BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EADCE8-BDBE-2848-8138-5E36931D028F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="600" windowWidth="24480" windowHeight="16100" xr2:uid="{A7D75AB7-B047-3448-8A7B-4FE35F9227AE}"/>
+    <workbookView xWindow="260" yWindow="940" windowWidth="24480" windowHeight="16100" xr2:uid="{A7D75AB7-B047-3448-8A7B-4FE35F9227AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8410" uniqueCount="1934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8411" uniqueCount="1935">
   <si>
     <t>id </t>
   </si>
@@ -5843,6 +5843,9 @@
   </si>
   <si>
     <t>KYRCQ606</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -6284,11 +6287,11 @@
       </c>
       <c r="J2" t="str">
         <f ca="1">CHAR(RANDBETWEEN(65,90))&amp;CHAR(RANDBETWEEN(65,90))&amp;CHAR(RANDBETWEEN(65,90))&amp;CHAR(RANDBETWEEN(65,90))&amp;CHAR(RANDBETWEEN(65,90))</f>
-        <v>YQSKM</v>
+        <v>GDLHC</v>
       </c>
       <c r="K2" t="str">
         <f ca="1">CONCATENATE(J2,RANDBETWEEN(111,999))</f>
-        <v>YQSKM772</v>
+        <v>GDLHC343</v>
       </c>
     </row>
     <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
@@ -18815,8 +18818,8 @@
       <c r="H434" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="I434">
-        <v>0</v>
+      <c r="I434" t="s">
+        <v>1934</v>
       </c>
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.2">
